--- a/resources/tool_kii_nutrition_service_provider_iphra_v2.xlsx
+++ b/resources/tool_kii_nutrition_service_provider_iphra_v2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saeed.rahman\Desktop\public_health_resources\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{291B28AB-7FA2-4FF1-9EAD-A50480239F53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CD1330E-1275-48AD-9219-4FC6C6B60C31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{27C29DD6-0256-4DF1-82F8-B613F9F4F125}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{27C29DD6-0256-4DF1-82F8-B613F9F4F125}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="309">
   <si>
     <t>type</t>
   </si>
@@ -1056,10 +1056,49 @@
     <t>Any other closing remarks by the interviewer?</t>
   </si>
   <si>
-    <t>48001, 48002, 48003, 48004</t>
-  </si>
-  <si>
     <t>strengths_weaknesses</t>
+  </si>
+  <si>
+    <t>14001, 14002, 14003, 14004</t>
+  </si>
+  <si>
+    <t>performance_indicators</t>
+  </si>
+  <si>
+    <t>enum_id</t>
+  </si>
+  <si>
+    <t>Team 1</t>
+  </si>
+  <si>
+    <t>Équipe 1</t>
+  </si>
+  <si>
+    <t>Team 2</t>
+  </si>
+  <si>
+    <t>Équipe 2</t>
+  </si>
+  <si>
+    <t>Team 3</t>
+  </si>
+  <si>
+    <t>Équipe 3</t>
+  </si>
+  <si>
+    <t>Team 4</t>
+  </si>
+  <si>
+    <t>Équipe 4</t>
+  </si>
+  <si>
+    <t>Team 5</t>
+  </si>
+  <si>
+    <t>Équipe 5</t>
+  </si>
+  <si>
+    <t>label::French (fr)</t>
   </si>
 </sst>
 </file>
@@ -1125,7 +1164,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1150,6 +1189,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1163,7 +1214,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1183,11 +1234,23 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1888,8 +1951,8 @@
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>46202</v>
+      <c r="A18" s="11">
+        <v>13704</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>39</v>
@@ -1908,8 +1971,8 @@
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>46202</v>
+      <c r="A19" s="11">
+        <v>13704</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>19</v>
@@ -1928,8 +1991,8 @@
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>46202</v>
+      <c r="A20" s="11">
+        <v>13704</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>64</v>
@@ -1948,8 +2011,8 @@
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>46202</v>
+      <c r="A21" s="11">
+        <v>13704</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>19</v>
@@ -1968,8 +2031,8 @@
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>46202</v>
+      <c r="A22" s="11">
+        <v>13704</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>23</v>
@@ -1985,8 +2048,8 @@
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>46202</v>
+      <c r="A23" s="11">
+        <v>13704</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>64</v>
@@ -1999,8 +2062,8 @@
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>46202</v>
+      <c r="A24" s="11">
+        <v>13704</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>19</v>
@@ -2013,8 +2076,8 @@
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>46202</v>
+      <c r="A25" s="11">
+        <v>13704</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>134</v>
@@ -2027,8 +2090,8 @@
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>46202</v>
+      <c r="A26" s="11">
+        <v>13704</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>19</v>
@@ -2041,8 +2104,8 @@
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>46202</v>
+      <c r="A27" s="11">
+        <v>13704</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>134</v>
@@ -2055,8 +2118,8 @@
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>46202</v>
+      <c r="A28" s="11">
+        <v>13704</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>19</v>
@@ -2069,8 +2132,8 @@
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>46202</v>
+      <c r="A29" s="11">
+        <v>13704</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>134</v>
@@ -2083,8 +2146,8 @@
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>46202</v>
+      <c r="A30" s="11">
+        <v>13704</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>19</v>
@@ -2097,8 +2160,8 @@
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>46202</v>
+      <c r="A31" s="11">
+        <v>13704</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>134</v>
@@ -2111,8 +2174,8 @@
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>46202</v>
+      <c r="A32" s="11">
+        <v>13704</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>19</v>
@@ -2125,8 +2188,8 @@
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>46301</v>
+      <c r="A33" s="11">
+        <v>13705</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>64</v>
@@ -2139,8 +2202,8 @@
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>46301</v>
+      <c r="A34" s="11">
+        <v>13705</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>19</v>
@@ -2153,8 +2216,8 @@
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>46301</v>
+      <c r="A35" s="11">
+        <v>13705</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>19</v>
@@ -2167,8 +2230,8 @@
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>46301</v>
+      <c r="A36" s="11">
+        <v>13705</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>134</v>
@@ -2181,8 +2244,8 @@
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>46301</v>
+      <c r="A37" s="11">
+        <v>13705</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>144</v>
@@ -2198,8 +2261,8 @@
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>46301</v>
+      <c r="A38" s="11">
+        <v>13705</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>19</v>
@@ -2212,8 +2275,8 @@
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <v>46301</v>
+      <c r="A39" s="11">
+        <v>13705</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>134</v>
@@ -2226,8 +2289,8 @@
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <v>46301</v>
+      <c r="A40" s="11">
+        <v>13705</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>144</v>
@@ -2243,8 +2306,8 @@
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <v>46301</v>
+      <c r="A41" s="11">
+        <v>13705</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>19</v>
@@ -2257,8 +2320,8 @@
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A42" s="2">
-        <v>46302</v>
+      <c r="A42" s="11">
+        <v>13706</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>64</v>
@@ -2271,8 +2334,8 @@
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A43" s="2">
-        <v>46302</v>
+      <c r="A43" s="11">
+        <v>13706</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>19</v>
@@ -2285,8 +2348,8 @@
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A44" s="2">
-        <v>46302</v>
+      <c r="A44" s="11">
+        <v>13706</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>19</v>
@@ -2299,8 +2362,8 @@
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A45" s="2">
-        <v>46302</v>
+      <c r="A45" s="11">
+        <v>13706</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>175</v>
@@ -2313,8 +2376,8 @@
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A46" s="2">
-        <v>46302</v>
+      <c r="A46" s="11">
+        <v>13706</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>19</v>
@@ -2327,8 +2390,8 @@
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A47" s="2">
-        <v>46303</v>
+      <c r="A47" s="11">
+        <v>13707</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>203</v>
@@ -2341,8 +2404,8 @@
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A48" s="2">
-        <v>46303</v>
+      <c r="A48" s="11">
+        <v>13707</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>19</v>
@@ -2355,8 +2418,8 @@
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A49" s="2">
-        <v>46303</v>
+      <c r="A49" s="11">
+        <v>13707</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>134</v>
@@ -2369,8 +2432,8 @@
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A50" s="2">
-        <v>46303</v>
+      <c r="A50" s="11">
+        <v>13707</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>19</v>
@@ -2386,8 +2449,8 @@
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A51">
-        <v>47002</v>
+      <c r="A51" s="11">
+        <v>13802</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>134</v>
@@ -2400,8 +2463,8 @@
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A52">
-        <v>47002</v>
+      <c r="A52" s="11">
+        <v>13802</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>19</v>
@@ -2417,8 +2480,8 @@
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A53">
-        <v>47002</v>
+      <c r="A53" s="11">
+        <v>13802</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>134</v>
@@ -2431,8 +2494,8 @@
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A54">
-        <v>47002</v>
+      <c r="A54" s="11">
+        <v>13802</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>19</v>
@@ -2448,8 +2511,8 @@
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A55">
-        <v>47201</v>
+      <c r="A55" s="11">
+        <v>13901</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>134</v>
@@ -2462,8 +2525,8 @@
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A56">
-        <v>47201</v>
+      <c r="A56" s="11">
+        <v>13901</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>19</v>
@@ -2479,8 +2542,8 @@
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A57">
-        <v>47201</v>
+      <c r="A57" s="11">
+        <v>13901</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>234</v>
@@ -2493,8 +2556,8 @@
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A58">
-        <v>47201</v>
+      <c r="A58" s="11">
+        <v>13901</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>19</v>
@@ -2507,8 +2570,8 @@
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A59">
-        <v>47201</v>
+      <c r="A59" s="11">
+        <v>13901</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>19</v>
@@ -2524,8 +2587,8 @@
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A60">
-        <v>47201</v>
+      <c r="A60" s="11">
+        <v>13901</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>19</v>
@@ -2541,8 +2604,8 @@
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A61">
-        <v>47201</v>
+      <c r="A61" s="11">
+        <v>13901</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>19</v>
@@ -2558,8 +2621,8 @@
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A62">
-        <v>47201</v>
+      <c r="A62" s="11">
+        <v>13901</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>19</v>
@@ -2575,8 +2638,8 @@
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A63">
-        <v>47201</v>
+      <c r="A63" s="11">
+        <v>13901</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>19</v>
@@ -2592,8 +2655,8 @@
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A64">
-        <v>17101</v>
+      <c r="A64" s="11">
+        <v>10703</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>134</v>
@@ -2606,8 +2669,8 @@
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A65">
-        <v>17101</v>
+      <c r="A65" s="11">
+        <v>10703</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>19</v>
@@ -2620,8 +2683,8 @@
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A66">
-        <v>17101</v>
+      <c r="A66" s="11">
+        <v>10703</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>19</v>
@@ -2638,11 +2701,14 @@
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>83</v>
       </c>
+      <c r="C67" s="2" t="s">
+        <v>296</v>
+      </c>
       <c r="D67" s="8" t="s">
         <v>274</v>
       </c>
@@ -2651,8 +2717,8 @@
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A68">
-        <v>48001</v>
+      <c r="A68" s="11">
+        <v>14001</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>19</v>
@@ -2668,8 +2734,8 @@
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A69">
-        <v>48002</v>
+      <c r="A69" s="11">
+        <v>14002</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>19</v>
@@ -2685,8 +2751,8 @@
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A70">
-        <v>48003</v>
+      <c r="A70" s="11">
+        <v>14003</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>19</v>
@@ -2702,8 +2768,8 @@
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A71">
-        <v>48004</v>
+      <c r="A71" s="11">
+        <v>14004</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>19</v>
@@ -2719,8 +2785,8 @@
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A72" s="2">
-        <v>48005</v>
+      <c r="A72" s="11">
+        <v>14005</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>19</v>
@@ -2736,14 +2802,14 @@
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A73" s="2">
-        <v>48005</v>
+      <c r="A73" s="11">
+        <v>14005</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D73" s="8" t="s">
         <v>285</v>
@@ -2753,8 +2819,8 @@
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A74" s="2">
-        <v>48005</v>
+      <c r="A74" s="11">
+        <v>14005</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>19</v>
@@ -2770,8 +2836,8 @@
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A75" s="2">
-        <v>48005</v>
+      <c r="A75" s="11">
+        <v>14005</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>19</v>
@@ -2845,7 +2911,7 @@
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="C8:C9">
-    <cfRule type="duplicateValues" dxfId="4" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="7"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2853,7 +2919,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D63B81B-C0DE-4D5C-B8D8-1821B93262B2}">
-  <dimension ref="A1:J72"/>
+  <dimension ref="A1:J77"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.85546875" style="2" customWidth="1"/>
@@ -2873,6 +2939,9 @@
       <c r="D1" s="6" t="s">
         <v>2</v>
       </c>
+      <c r="E1" s="12" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="9">
@@ -3105,95 +3174,95 @@
         <v>10000</v>
       </c>
       <c r="B16" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="C16" s="9">
+        <v>1</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="C17" s="9">
+        <v>2</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="C18" s="9">
+        <v>3</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="C19" s="9">
+        <v>4</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="C20" s="9">
+        <v>5</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B21" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C21" s="9" t="s">
         <v>115</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="9">
-        <v>10000</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="9">
-        <v>10000</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="9">
-        <v>10000</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="9">
-        <v>10000</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="9">
-        <v>10000</v>
-      </c>
-      <c r="B21" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>123</v>
       </c>
       <c r="D21" s="9" t="s">
         <v>116</v>
@@ -3202,15 +3271,15 @@
         <v>117</v>
       </c>
     </row>
-    <row r="22" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="9">
         <v>10000</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="D22" s="9" t="s">
         <v>116</v>
@@ -3219,15 +3288,15 @@
         <v>117</v>
       </c>
     </row>
-    <row r="23" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="9">
         <v>10000</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="D23" s="9" t="s">
         <v>116</v>
@@ -3236,15 +3305,15 @@
         <v>117</v>
       </c>
     </row>
-    <row r="24" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="9">
         <v>10000</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="D24" s="9" t="s">
         <v>116</v>
@@ -3253,15 +3322,15 @@
         <v>117</v>
       </c>
     </row>
-    <row r="25" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="9">
         <v>10000</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D25" s="9" t="s">
         <v>116</v>
@@ -3270,15 +3339,15 @@
         <v>117</v>
       </c>
     </row>
-    <row r="26" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="9">
         <v>10000</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="D26" s="9" t="s">
         <v>116</v>
@@ -3287,15 +3356,15 @@
         <v>117</v>
       </c>
     </row>
-    <row r="27" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="9">
         <v>10000</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="D27" s="9" t="s">
         <v>116</v>
@@ -3304,650 +3373,738 @@
         <v>117</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="9">
         <v>10000</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C33" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D33" s="2" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="9">
-        <v>10000</v>
-      </c>
-      <c r="B29" s="3" t="s">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C34" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D34" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>46202</v>
-      </c>
-      <c r="B30" s="3" t="s">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="11">
+        <v>13704</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C35" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D35" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>46202</v>
-      </c>
-      <c r="B31" s="3" t="s">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="11">
+        <v>13704</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C36" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="D36" s="2" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>46202</v>
-      </c>
-      <c r="B32" s="3" t="s">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="11">
+        <v>13704</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C37" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="D37" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="J32" s="2" t="s">
+      <c r="J37" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>46202</v>
-      </c>
-      <c r="B33" s="3" t="s">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="11">
+        <v>13704</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C38" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="D38" s="2" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>46202</v>
-      </c>
-      <c r="B34" s="3" t="s">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="11">
+        <v>13704</v>
+      </c>
+      <c r="B39" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C39" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="D39" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>46202</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>46202</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>46202</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>46202</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <v>46202</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <v>46202</v>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="11">
+        <v>13704</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C40" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="11">
+        <v>13704</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="11">
+        <v>13704</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="11">
+        <v>13704</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="11">
+        <v>13704</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="11">
+        <v>13704</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C45" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="D45" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <v>46301</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42">
-        <v>46301</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43">
-        <v>46301</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44">
-        <v>46301</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45">
-        <v>46301</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46">
-        <v>46301</v>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="11">
+        <v>13705</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>145</v>
       </c>
       <c r="C46" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" s="11">
+        <v>13705</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" s="11">
+        <v>13705</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="11">
+        <v>13705</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="11">
+        <v>13705</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="11">
+        <v>13705</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C51" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D46" s="2" t="s">
+      <c r="D51" s="2" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="2">
-        <v>46302</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="2">
-        <v>46302</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="2">
-        <v>46302</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="2">
-        <v>46302</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="2">
-        <v>46302</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>181</v>
-      </c>
-    </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="2">
-        <v>46302</v>
+      <c r="A52" s="11">
+        <v>13706</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>176</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="2">
-        <v>46302</v>
+      <c r="A53" s="11">
+        <v>13706</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>176</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="2">
-        <v>46302</v>
+      <c r="A54" s="11">
+        <v>13706</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>176</v>
       </c>
       <c r="C54" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="11">
+        <v>13706</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="11">
+        <v>13706</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="11">
+        <v>13706</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="11">
+        <v>13706</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="11">
+        <v>13706</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C59" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D54" s="2" t="s">
+      <c r="D59" s="2" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="2">
-        <v>46303</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="2">
-        <v>46303</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="2">
-        <v>46303</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="2">
-        <v>46303</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="2">
-        <v>46303</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>209</v>
-      </c>
-    </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" s="2">
-        <v>46303</v>
+      <c r="A60" s="11">
+        <v>13707</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>216</v>
       </c>
       <c r="C60" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="11">
+        <v>13707</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="11">
+        <v>13707</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" s="11">
+        <v>13707</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" s="11">
+        <v>13707</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="11">
+        <v>13707</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C65" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D60" s="2" t="s">
+      <c r="D65" s="2" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61">
-        <v>47201</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="D61" s="4" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62">
-        <v>47201</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="D62" s="4" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63">
-        <v>47201</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="D63" s="4" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64">
-        <v>47201</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="D64" s="4" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65">
-        <v>47201</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="D65" s="4" t="s">
-        <v>240</v>
-      </c>
-    </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66">
-        <v>47201</v>
+      <c r="A66" s="11">
+        <v>13901</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>235</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67">
-        <v>47201</v>
+      <c r="A67" s="11">
+        <v>13901</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>235</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A68">
-        <v>47201</v>
+      <c r="A68" s="11">
+        <v>13901</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>235</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69">
-        <v>47201</v>
+      <c r="A69" s="11">
+        <v>13901</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>235</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70">
-        <v>47201</v>
+      <c r="A70" s="11">
+        <v>13901</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>235</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A71">
-        <v>47201</v>
+      <c r="A71" s="11">
+        <v>13901</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>235</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>29</v>
+        <v>254</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>40</v>
+        <v>241</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72">
-        <v>47201</v>
+      <c r="A72" s="11">
+        <v>13901</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>235</v>
       </c>
       <c r="C72" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="11">
+        <v>13901</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" s="11">
+        <v>13901</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" s="11">
+        <v>13901</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" s="11">
+        <v>13901</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" s="11">
+        <v>13901</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C77" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="D72" s="4" t="s">
+      <c r="D77" s="4" t="s">
         <v>105</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C4:C6">
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C7:C10">
     <cfRule type="duplicateValues" dxfId="3" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C7:C10">
+  <conditionalFormatting sqref="C11:C12">
     <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C11:C12">
+  <conditionalFormatting sqref="C21:C32">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C16:C27">
+  <conditionalFormatting sqref="C16:C20">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
